--- a/ressources/Maquette_Agenda.xlsx
+++ b/ressources/Maquette_Agenda.xlsx
@@ -1,21 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\2_Enseignement\2026-2027\M2_Carthageo\CALENDRIER\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3A048D-4C58-40B4-88C5-7701E3D1A809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="7"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Feuil1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -27,211 +22,244 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="133">
   <si>
-    <t>SEMESTRE</t>
-  </si>
-  <si>
-    <t>UE</t>
-  </si>
-  <si>
-    <t>CODE</t>
-  </si>
-  <si>
-    <t>Matiere</t>
-  </si>
-  <si>
-    <t>shortName</t>
-  </si>
-  <si>
-    <t>Enseignant.e</t>
-  </si>
-  <si>
-    <t>UE 1 : Stages de mise à niveau</t>
-  </si>
-  <si>
-    <t>H5I40119</t>
-  </si>
-  <si>
-    <t>Logiciels de cartographie</t>
-  </si>
-  <si>
-    <t>MaN Illustrator</t>
-  </si>
-  <si>
-    <t>Marie Jolivet et Aurélie Boissière</t>
-  </si>
-  <si>
-    <t>MaN Carto</t>
-  </si>
-  <si>
-    <t>Olivier Finance</t>
-  </si>
-  <si>
-    <t>H5I40319</t>
-  </si>
-  <si>
-    <t>Logiciels de statistiques et d'analyse spatiale</t>
-  </si>
-  <si>
-    <t>MaN R</t>
-  </si>
-  <si>
-    <t>Hadrien Commenges</t>
-  </si>
-  <si>
-    <t>H5I40519</t>
-  </si>
-  <si>
-    <t>Analyse des données</t>
-  </si>
-  <si>
-    <t>MaN AnaDon</t>
-  </si>
-  <si>
-    <t>Mattia Bunel</t>
-  </si>
-  <si>
-    <t>UE 2 :  Bases de données et interopérabilité</t>
-  </si>
-  <si>
-    <t>H5I40719</t>
-  </si>
-  <si>
-    <t>Bases de données spatiales</t>
-  </si>
-  <si>
-    <t>ArcGIS-Auto</t>
-  </si>
-  <si>
-    <t>GeoData</t>
-  </si>
-  <si>
-    <t>BD Spatiales</t>
-  </si>
-  <si>
-    <t>H5I40919</t>
-  </si>
-  <si>
-    <t>Normalisation et interopérabilité</t>
-  </si>
-  <si>
-    <t>Normes &amp; Métadonnées</t>
+    <t xml:space="preserve">SEMESTRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CODE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matiere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shortName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enseignant.e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UE 1 : Stages de mise à niveau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H5I40119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logiciels de cartographie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaN Illustrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marie Jolivet et Aurélie Boissière</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaN Carto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olivier Finance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H5I40319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logiciels de statistiques et d'analyse spatiale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaN R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadrien Commenges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H5I40519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analyse des données</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaN AnaDon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mattia Bunel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UE 2 :  Bases de données et interopérabilité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H5I40719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bases de données spatiales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ArcGIS-Auto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GeoData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BD Spatiales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H5I40919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normalisation et interopérabilité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normes &amp; Métadonnées</t>
   </si>
   <si>
     <t xml:space="preserve">H5I41125 </t>
   </si>
   <si>
-    <t>Transformations automatisées (FME)</t>
-  </si>
-  <si>
-    <t>FME</t>
-  </si>
-  <si>
-    <t>Evals FME</t>
-  </si>
-  <si>
-    <t>UE 3 : SIG et développements informatiques</t>
-  </si>
-  <si>
-    <t>H5I41319</t>
-  </si>
-  <si>
-    <t>Initiation à la programmation (algorithmie)</t>
-  </si>
-  <si>
-    <t>AlgoPy</t>
-  </si>
-  <si>
-    <t>H5I41519</t>
-  </si>
-  <si>
-    <t>Développements sous SIG</t>
-  </si>
-  <si>
-    <t>Info &amp; SIG</t>
-  </si>
-  <si>
-    <t>UE 4 : Analyse spatiale</t>
+    <t xml:space="preserve">Transformations automatisées (FME)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evals FME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UE 3 : SIG et développements informatiques</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H5I41319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initiation à la programmation (algorithmie)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoPy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H5I41519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Développements sous SIG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Info &amp; SIG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UE 4 : Analyse spatiale</t>
   </si>
   <si>
     <t xml:space="preserve">H5I20925 </t>
   </si>
   <si>
-    <t>Stage d'analyse de données avec R</t>
-  </si>
-  <si>
-    <t>Stage AnaSpa</t>
-  </si>
-  <si>
-    <t>Hadrien Commenges, Pierre Pistre et Claude Grasland</t>
-  </si>
-  <si>
-    <t>H5G43515</t>
-  </si>
-  <si>
-    <t>Analyse spatiale et statistiques</t>
-  </si>
-  <si>
-    <t>AnaSpa Stats HC</t>
-  </si>
-  <si>
-    <t>AnaSpa Stats RC</t>
-  </si>
-  <si>
-    <t>Robin Cura</t>
-  </si>
-  <si>
-    <t>H5G43715</t>
-  </si>
-  <si>
-    <t>Analyse spatiale et SIG</t>
-  </si>
-  <si>
-    <t>AnaSpa SIG RC</t>
-  </si>
-  <si>
-    <t>AnaSpa SIG JM</t>
-  </si>
-  <si>
-    <t>Juliette Morel</t>
-  </si>
-  <si>
-    <t>UE 5 : Cartographie</t>
+    <t xml:space="preserve">Stage d'analyse de données avec R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage AnaSpa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadrien Commenges, Pierre Pistre et Olivier Finance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H5G43515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analyse spatiale et statistiques</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AnaSpa Stats HC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AnaSpa Stats RC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robin Cura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H5G43715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analyse spatiale et SIG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AnaSpa SIG RC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AnaSpa SIG JM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juliette Morel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UE 5 : Cartographie</t>
   </si>
   <si>
     <t xml:space="preserve">H5I41725 </t>
   </si>
   <si>
-    <t>Séminaire Histoire et pratique de la cartographie</t>
-  </si>
-  <si>
-    <t>H5I41919</t>
-  </si>
-  <si>
-    <t>Sémiologie graphique statique et dynamique</t>
-  </si>
-  <si>
-    <t>Spectacle "Carto!"</t>
-  </si>
-  <si>
-    <t>Carto OF</t>
-  </si>
-  <si>
-    <t>Carto MJ</t>
-  </si>
-  <si>
-    <t>Marie Jolivet</t>
-  </si>
-  <si>
-    <t>CartoDyn OF</t>
-  </si>
-  <si>
-    <t>CartoDyn MJ</t>
-  </si>
-  <si>
-    <t>CartoDyn JM</t>
-  </si>
-  <si>
-    <t>UE 6 : Géomatique : Recherche et applications</t>
+    <t xml:space="preserve">Séminaire Histoire et pratique de la cartographie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiC 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emmanuelle Vagnon-Chureau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiC 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiC 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eve Netchine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiC 4 BNF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olivier Loiseaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiC 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Françoise Bahoken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiC 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicolas Lambert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H5I41919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sémiologie graphique statique et dynamique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spectacle "Carto!"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carto OF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carto MJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marie Jolivet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CartoDyn OF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CartoDyn MJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CartoDyn JM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UE 6 : Géomatique : Recherche et applications</t>
   </si>
   <si>
     <t xml:space="preserve">H5I21715 </t>
@@ -240,203 +268,189 @@
     <t xml:space="preserve">Séminaire de recherche : Approches thématiques </t>
   </si>
   <si>
-    <t>Séminaire Recherche</t>
-  </si>
-  <si>
-    <t>Marie Gibert</t>
-  </si>
-  <si>
-    <t>H5I42319</t>
-  </si>
-  <si>
-    <t>Rencontres métiers - BILINGUE</t>
-  </si>
-  <si>
-    <t>H5I42119</t>
-  </si>
-  <si>
-    <t>Répondre à un appel d'offre</t>
-  </si>
-  <si>
-    <t>AO</t>
-  </si>
-  <si>
-    <t>UE 1 : Projets cartographiques</t>
-  </si>
-  <si>
-    <t>H5G40215</t>
-  </si>
-  <si>
-    <t>Projet de cartographie éditoriale - BILINGUE</t>
-  </si>
-  <si>
-    <t>Projet Plaquette</t>
-  </si>
-  <si>
-    <t>Plaquette Anglais</t>
-  </si>
-  <si>
-    <t>H5G40615</t>
-  </si>
-  <si>
-    <t>Projet transversal d'analyse spatiale</t>
-  </si>
-  <si>
-    <t>Projet Transversal</t>
-  </si>
-  <si>
-    <t>Robin Cura et Juliette Morel</t>
-  </si>
-  <si>
-    <t>UE 2 :  Géovisualisation</t>
-  </si>
-  <si>
-    <t>H5I40419</t>
-  </si>
-  <si>
-    <t>Introduction aux langages du Web</t>
-  </si>
-  <si>
-    <t>CartoWeb 1</t>
-  </si>
-  <si>
-    <t>H5I40819</t>
-  </si>
-  <si>
-    <t>Principes de géovisualisation</t>
-  </si>
-  <si>
-    <t>GéoViz</t>
-  </si>
-  <si>
-    <t>H5I41019</t>
-  </si>
-  <si>
-    <t>Diffusion cartographique sur Internet (webmapping)</t>
-  </si>
-  <si>
-    <t>CartoWeb 2</t>
-  </si>
-  <si>
-    <t>Hors Maquette</t>
-  </si>
-  <si>
-    <t>Journée du Bureau d’Aide à l’Insertion Professionnelle</t>
-  </si>
-  <si>
-    <t>BAIP</t>
-  </si>
-  <si>
-    <t>Rentrée</t>
-  </si>
-  <si>
-    <t>Tou.te.s</t>
-  </si>
-  <si>
-    <t>Soutenances M2 2025/2026</t>
-  </si>
-  <si>
-    <t>Soutenances M2</t>
-  </si>
-  <si>
-    <t>Bilan année 2026/2027</t>
-  </si>
-  <si>
-    <t>Bilan année</t>
-  </si>
-  <si>
-    <t>Atelier Cartographie Experimentale</t>
-  </si>
-  <si>
-    <t>Accueil GeoData Paris</t>
-  </si>
-  <si>
-    <t>Accueil GeoData</t>
-  </si>
-  <si>
-    <t>République des Cartes</t>
-  </si>
-  <si>
-    <t>HiC 1</t>
-  </si>
-  <si>
-    <t>Emmanuelle Vagnon-Chureau</t>
-  </si>
-  <si>
-    <t>HiC 2</t>
-  </si>
-  <si>
-    <t>HiC 3</t>
-  </si>
-  <si>
-    <t>HiC BNF</t>
-  </si>
-  <si>
-    <t>HiC 5</t>
-  </si>
-  <si>
-    <t>Françoise Bahoken</t>
-  </si>
-  <si>
-    <t>HiC 6</t>
-  </si>
-  <si>
-    <t>Nicolas Lambert</t>
-  </si>
-  <si>
-    <t>RencM 1</t>
-  </si>
-  <si>
-    <t>Henry Ciesielski</t>
-  </si>
-  <si>
-    <t>RencM 2</t>
-  </si>
-  <si>
-    <t>Logan Savage</t>
-  </si>
-  <si>
-    <t>RencM 3</t>
-  </si>
-  <si>
-    <t>Guilhain Averlant</t>
-  </si>
-  <si>
-    <t>RencM 6</t>
-  </si>
-  <si>
-    <t>Anne Lacambre</t>
-  </si>
-  <si>
-    <t>Olivier Loiseaux</t>
-  </si>
-  <si>
-    <t>RencM 4</t>
-  </si>
-  <si>
-    <t>Maeve de France</t>
-  </si>
-  <si>
-    <t>RencM 5</t>
-  </si>
-  <si>
-    <t>Ghislaine Convers</t>
-  </si>
-  <si>
-    <t>Eve Netchine</t>
+    <t xml:space="preserve">Séminaire Recherche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marie Gibert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H5I42319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rencontres métiers - BILINGUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RencM 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Henry Ciesielski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RencM 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logan Savage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RencM 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guilhain Averlant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RencM 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maeve de France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RencM 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ghislaine Convers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RencM 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anne Lacambre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H5I42119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Répondre à un appel d'offre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UE 1 : Projets cartographiques</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H5G40215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projet de cartographie éditoriale - BILINGUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projet Plaquette</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plaquette Anglais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H5G40615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projet transversal d'analyse spatiale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projet Transversal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robin Cura et Juliette Morel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UE 2 :  Géovisualisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H5I40419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Introduction aux langages du Web</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CartoWeb 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H5I40819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principes de géovisualisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GéoViz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H5I41019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diffusion cartographique sur Internet (webmapping)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CartoWeb 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hors Maquette</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journée du Bureau d’Aide à l’Insertion Professionnelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rentrée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tou.te.s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soutenances M2 2025/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soutenances M2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bilan année 2026/2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bilan année</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atelier Cartographie Experimentale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil GeoData Paris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accueil GeoData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">République des Cartes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="@"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -448,7 +462,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -456,37 +470,62 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -528,12 +567,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -565,7 +604,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -589,7 +628,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -649,29 +688,30 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="2" max="2" width="46" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="48.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="49" style="1" customWidth="1"/>
-    <col min="6" max="6" width="31.28515625" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="48.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="31.29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -691,8 +731,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -711,8 +751,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -731,8 +771,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -751,8 +791,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -771,8 +811,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -791,8 +831,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -811,8 +851,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -831,8 +871,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -851,8 +891,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -871,8 +911,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -891,8 +931,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -911,8 +951,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -931,8 +971,8 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -951,8 +991,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -971,8 +1011,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -991,8 +1031,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -1011,8 +1051,8 @@
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -1025,14 +1065,14 @@
         <v>58</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>110</v>
+        <v>59</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -1045,14 +1085,14 @@
         <v>58</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>112</v>
+        <v>61</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -1065,14 +1105,14 @@
         <v>58</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -1085,14 +1125,14 @@
         <v>58</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -1105,14 +1145,14 @@
         <v>58</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
@@ -1125,554 +1165,559 @@
         <v>58</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C37" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>25</v>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>